--- a/1.PromptsUpdate.xlsx
+++ b/1.PromptsUpdate.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,6 +535,23 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-21 11:40</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>"모호함·억지·오류·환각 검토" 요청을 무맥락 신규 에이전트 수행 방식 스킬로 제작 요청 + 설계 결정 4건 응답(2모드 범위/웹 출처·수치 한정/단일+트리아지/자문 전용)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>fresh-eyes-auditor 생성: Step0 파일범위 확정(모드 A/B)→Step1 오염방지 스폰(경로+루브릭만)→Step2 인용검증 트리아지(MISQUOTE/JUSTIFIED/TRIVIAL)→Step3 자문 리포트+라우팅. 리스크 3건(범위 재정의·false positive·검증자 환각) 설계 반영. save_skill로 계정 설치 완료.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
